--- a/data/output/2025/evaluasi_17.xlsx
+++ b/data/output/2025/evaluasi_17.xlsx
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,34 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Tengah</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -807,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,6 +951,34 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1771</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Bengkulu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -937,7 +993,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,6 +1165,90 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1702</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Rejang Lebong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8729238242516244</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1702</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Rejang Lebong</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>48.84550670407879</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1702</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Rejang Lebong</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1263,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1491,6 +1631,62 @@
       <c r="F13" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Seluma</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>24.53333333333083</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Seluma</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1565,6 +1761,258 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.1889075457898</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>44.38497150377988</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.6594758075852074</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.1126031033154173</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.052372984218171</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-1.323023443513366</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.09492134574612</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.4637570537223007</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1579,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1667,6 +2115,202 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>62.31824739574174</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.7447396548973558</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.963681871305601</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.094553990470887</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.8912915141112276</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-5.77035610042749</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q4-25_prov vs implisit_y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1681,7 +2325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +2385,118 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3228388604230988</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaur</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>26.58044893944848</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaur</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaur</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.002117218622749312</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q4-25_prov vs implisit_q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1755,7 +2511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1871,6 +2627,34 @@
       <c r="F4" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mukomuko</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1885,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2029,6 +2813,62 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1707</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebong</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1707</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebong</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.239335406533611</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2043,7 +2883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,6 +3002,34 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1708</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepahiang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
